--- a/Modbus Codes.xlsx
+++ b/Modbus Codes.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Evap Unit</t>
   </si>
   <si>
-    <t xml:space="preserve">00 18 00 20 </t>
+    <t xml:space="preserve">00 18 00 20 (CRC C4 26)</t>
   </si>
   <si>
     <t xml:space="preserve">40 00 02 00 02 00 0E 00 2E 03 YY 0D ZZ 00 00 00 00 00 F8 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 00 1D 2E B1 00 00 00 00 00 00 00 00 30 XX 00 00 00 00 00 00 WW QQ UU RR 00 TT
@@ -1296,16 +1296,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="37.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="160.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="123.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="123.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="255.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1883,7 +1883,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>76</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
         <v>76</v>
       </c>

--- a/Modbus Codes.xlsx
+++ b/Modbus Codes.xlsx
@@ -100,7 +100,7 @@
 2 15 16</t>
   </si>
   <si>
-    <t xml:space="preserve">00 00 00 12 </t>
+    <t xml:space="preserve">00 00 00 12 (CRC C5 F4)</t>
   </si>
   <si>
     <r>
@@ -1296,7 +1296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
